--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484746_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484746_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.617000000000001</v>
+        <v>8.604799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9509</v>
+        <v>6.9123</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6661</v>
+        <v>1.6926</v>
       </c>
       <c r="G2" t="n">
         <v>8.3811</v>
@@ -610,13 +610,13 @@
         <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5003</v>
+        <v>0.4881</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3709</v>
+        <v>0.3322</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1294</v>
+        <v>0.1559</v>
       </c>
       <c r="V2" t="n">
         <v>1.2452</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3409</v>
+        <v>3.6615</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6674</v>
+        <v>-0.0332</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6735</v>
+        <v>3.6947</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9486</v>
@@ -688,13 +688,13 @@
         <v>2.4531</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4784</v>
+        <v>0.7991</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.2052</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5727</v>
+        <v>0.5939</v>
       </c>
       <c r="V3" t="n">
         <v>4.3772</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.498</v>
+        <v>0.8021</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4372</v>
+        <v>-1.0273</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9352</v>
+        <v>1.8294</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5764</v>
@@ -844,13 +844,13 @@
         <v>1.1322</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2822</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3375</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6197</v>
+        <v>0.5139</v>
       </c>
       <c r="V5" t="n">
         <v>1.547</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2575</v>
+        <v>-0.1193</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4501</v>
+        <v>-1.3913</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1926</v>
+        <v>1.272</v>
       </c>
       <c r="G6" t="n">
         <v>0.5431</v>
@@ -922,13 +922,13 @@
         <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3127</v>
+        <v>0.4509</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0617</v>
+        <v>0.1205</v>
       </c>
       <c r="U6" t="n">
-        <v>0.251</v>
+        <v>0.3304</v>
       </c>
       <c r="V6" t="n">
         <v>0.9624</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MARTIN MARTINEZ</t>
+          <t>G. GARCIA CARCASES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.504</v>
+        <v>-0.3522</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4909</v>
+        <v>0.423</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9948</v>
+        <v>-0.7753</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0207</v>
+        <v>-0.0004</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3905</v>
+        <v>-0.9986</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6302</v>
+        <v>0.9982</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4315</v>
+        <v>1.1811</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1479</v>
+        <v>-0.1847</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2836</v>
+        <v>1.3658</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5891999999999999</v>
+        <v>-1.1815</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2426</v>
+        <v>-0.8139</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3466</v>
+        <v>-0.3676</v>
       </c>
       <c r="P7" t="n">
+        <v>0.7548</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.1887</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.9435</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1663</v>
+        <v>-1.1066</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0029</v>
+        <v>-0.5694</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1692</v>
+        <v>-0.5372</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1696</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.6398</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7191</v>
+        <v>-0.6216</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1505</v>
+        <v>-0.0182</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5383</v>
@@ -1078,13 +1078,13 @@
         <v>0.3774</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4068</v>
+        <v>-0.1771</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2352</v>
+        <v>-0.1377</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1716</v>
+        <v>-0.0394</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3018</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GARCIA CARCASES</t>
+          <t>M. MARTIN MARTINEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9498</v>
+        <v>-0.6871</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1694</v>
+        <v>0.4136</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1192</v>
+        <v>-1.1006</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0004</v>
+        <v>2.0207</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9986</v>
+        <v>0.3905</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9982</v>
+        <v>1.6302</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1811</v>
+        <v>1.4315</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1847</v>
+        <v>0.1479</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3658</v>
+        <v>1.2836</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1815</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8139</v>
+        <v>0.2426</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3676</v>
+        <v>0.3466</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.1887</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.9435</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.7548</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-0.1887</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.9435</v>
-      </c>
       <c r="S9" t="n">
-        <v>-1.7042</v>
+        <v>-0.3495</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.823</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8812</v>
+        <v>-0.2751</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.1696</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1114</v>
+        <v>-1.1661</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8317</v>
+        <v>-2.0451</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6681</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8965</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1582</v>
+        <v>-0.3716</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7382</v>
+        <v>-0.5795</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2452</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5181</v>
+        <v>-1.4388</v>
       </c>
       <c r="E11" t="n">
         <v>-0.093</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4252</v>
+        <v>-1.3458</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7721</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1235</v>
+        <v>-0.0441</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0529</v>
+        <v>0.1323</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6226</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9756</v>
+        <v>-2.7611</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3585</v>
+        <v>-4.4615</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3829</v>
+        <v>1.7003</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6395999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8641</v>
+        <v>-0.6496</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4574</v>
+        <v>-0.5603</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4067</v>
+        <v>-0.0893</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3398</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9715</v>
+        <v>-4.7237</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.827</v>
+        <v>-2.6322</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1445</v>
+        <v>-2.0916</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6271</v>
@@ -1468,13 +1468,13 @@
         <v>0.5661</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7783</v>
+        <v>-0.5305</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3527</v>
+        <v>-0.1579</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4256</v>
+        <v>-0.3727</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2452</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.083300000000004</v>
+        <v>3.965099999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.653200000000001</v>
+        <v>-1.7715</v>
       </c>
       <c r="F14" t="n">
-        <v>5.7364</v>
+        <v>5.736499999999999</v>
       </c>
       <c r="G14" t="n">
         <v>7.959099999999999</v>
@@ -1546,13 +1546,13 @@
         <v>12.2655</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3661</v>
+        <v>-1.4842</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1992</v>
+        <v>-1.3174</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1668</v>
+        <v>-0.1667999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.2076</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5379</v>
+        <v>5.5096</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2029</v>
+        <v>3.5209</v>
       </c>
       <c r="F15" t="n">
-        <v>2.335</v>
+        <v>1.9887</v>
       </c>
       <c r="G15" t="n">
         <v>3.7342</v>
@@ -1624,13 +1624,13 @@
         <v>2.6418</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7089</v>
+        <v>0.6806</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6677</v>
+        <v>-0.0143</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0412</v>
+        <v>0.6949</v>
       </c>
       <c r="V15" t="n">
         <v>-1.547</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8785</v>
+        <v>3.7589</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2369</v>
+        <v>2.8431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4216</v>
+        <v>1.9203</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.2738</v>
+        <v>-0.1949</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6953</v>
+        <v>2.1152</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0732</v>
+        <v>2.2797</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.7775</v>
+        <v>0.8146</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8507</v>
+        <v>1.4651</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6516</v>
+        <v>-0.3594</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4963</v>
+        <v>-1.0095</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8447</v>
+        <v>0.6501</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5661</v>
+        <v>2.2644</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4531</v>
+        <v>3.2079</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0909</v>
+        <v>-0.3202</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2585</v>
+        <v>-0.3609</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8325</v>
+        <v>0.0407</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7999000000000001</v>
+        <v>-0.1055</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7922</v>
+        <v>1.8678</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.9923</v>
+        <v>-1.9733</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5237</v>
+        <v>3.2939</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1611</v>
+        <v>2.6523</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3626</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9203</v>
+        <v>0.4216</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1949</v>
+        <v>-4.2738</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1152</v>
+        <v>4.6953</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2797</v>
+        <v>1.0732</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8146</v>
+        <v>-2.7775</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4651</v>
+        <v>3.8507</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3594</v>
+        <v>-0.6516</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0095</v>
+        <v>-1.4963</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6501</v>
+        <v>0.8447</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2644</v>
+        <v>0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2079</v>
+        <v>2.4531</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5555</v>
+        <v>1.5063</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0429</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5125</v>
+        <v>0.8325</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1055</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8678</v>
+        <v>2.7922</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.9733</v>
+        <v>-1.9923</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4955</v>
+        <v>1.7917</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0164</v>
+        <v>-2.0882</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5119</v>
+        <v>3.8799</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1859</v>
@@ -1858,13 +1858,13 @@
         <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6248</v>
+        <v>0.921</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>0.5982</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0452</v>
+        <v>0.3228</v>
       </c>
       <c r="V18" t="n">
         <v>0.3018</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5987</v>
+        <v>0.5723</v>
       </c>
       <c r="E20" t="n">
         <v>0.8932</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2945</v>
+        <v>-0.3209</v>
       </c>
       <c r="G20" t="n">
         <v>0.7463</v>
@@ -2014,13 +2014,13 @@
         <v>0.3774</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5249</v>
+        <v>-0.5514</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4115</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1134</v>
+        <v>-0.1399</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8527</v>
+        <v>-0.7131</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1747</v>
+        <v>-1.9799</v>
       </c>
       <c r="F21" t="n">
-        <v>1.322</v>
+        <v>1.2667</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3692</v>
@@ -2092,13 +2092,13 @@
         <v>2.4531</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5967</v>
+        <v>-0.4571</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7613</v>
+        <v>-0.5665</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1647</v>
+        <v>0.1094</v>
       </c>
       <c r="V21" t="n">
         <v>1.547</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9741</v>
+        <v>-1.2135</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3661</v>
+        <v>-0.6584</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.608</v>
+        <v>-0.5551</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9741</v>
@@ -2170,13 +2170,13 @@
         <v>0.3774</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0869</v>
+        <v>0.8475</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1993</v>
+        <v>0.2522</v>
       </c>
       <c r="V22" t="n">
         <v>-0.4643</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3421</v>
+        <v>-3.0312</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2539</v>
+        <v>-1.5462</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0882</v>
+        <v>-1.4851</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9939</v>
@@ -2248,13 +2248,13 @@
         <v>0.7548</v>
       </c>
       <c r="S23" t="n">
-        <v>0.512</v>
+        <v>-0.1771</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2323</v>
+        <v>-0.5246</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7443</v>
+        <v>0.3475</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6715</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. HORRACH SANCHEZ</t>
+          <t>A. SUCH LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7429</v>
+        <v>-3.1346</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7631</v>
+        <v>-2.8065</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9799</v>
+        <v>-0.3281</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5801</v>
+        <v>-1.6318</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.6276</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7106</v>
+        <v>-1.0042</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.4103</v>
+        <v>-0.316</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4805</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.8664</v>
+        <v>0.1645</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1697</v>
+        <v>-1.3158</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3256</v>
+        <v>-0.1471</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8442</v>
+        <v>-1.1687</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4838</v>
+        <v>0.6975</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3527</v>
+        <v>0.34</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1311</v>
+        <v>0.3574</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6226</v>
+        <v>-0.1245</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6226</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. SUCH LOPEZ</t>
+          <t>I. HORRACH SANCHEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4793</v>
+        <v>-3.3087</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7808</v>
+        <v>-2.2759</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6984</v>
+        <v>-1.0328</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6318</v>
+        <v>-3.5801</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6276</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0042</v>
+        <v>-2.7106</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.316</v>
+        <v>-2.4103</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4805</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1645</v>
+        <v>-1.8664</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3158</v>
+        <v>-1.1697</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1471</v>
+        <v>-0.3256</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1687</v>
+        <v>-0.8442</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0757</v>
+        <v>0.9435</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6472</v>
+        <v>-0.0495</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6343</v>
+        <v>0.1344</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0129</v>
+        <v>-0.184</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1245</v>
+        <v>-0.6226</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1245</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.3601</v>
+        <v>-6.5927</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.5094</v>
+        <v>-4.9248</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8507</v>
+        <v>-1.6679</v>
       </c>
       <c r="G26" t="n">
         <v>-4.6803</v>
@@ -2482,13 +2482,13 @@
         <v>1.3209</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8494</v>
+        <v>-0.082</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8818</v>
+        <v>-0.2972</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0324</v>
+        <v>0.2152</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3208</v>
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.083000000000001</v>
+        <v>-2.4335</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.7364</v>
+        <v>-5.736499999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>2.6534</v>
+        <v>3.302799999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.959</v>
+        <v>-7.959000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>-8.608599999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6494999999999984</v>
+        <v>0.6494999999999975</v>
       </c>
       <c r="J27" t="n">
         <v>-0.07060000000000066</v>
@@ -2545,10 +2545,10 @@
         <v>-7.888299999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>-6.918</v>
+        <v>-6.917999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.9704999999999999</v>
+        <v>-0.9705</v>
       </c>
       <c r="P27" t="n">
         <v>4.7175</v>
@@ -2560,13 +2560,13 @@
         <v>16.983</v>
       </c>
       <c r="S27" t="n">
-        <v>2.366000000000001</v>
+        <v>3.0156</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1669999999999999</v>
+        <v>0.1668000000000002</v>
       </c>
       <c r="U27" t="n">
-        <v>2.1993</v>
+        <v>2.8487</v>
       </c>
       <c r="V27" t="n">
         <v>-2.2075</v>
@@ -2575,7 +2575,7 @@
         <v>6.4328</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.640300000000002</v>
+        <v>-8.6403</v>
       </c>
     </row>
   </sheetData>
